--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -4203,7 +4203,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4413,6 +4413,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4422,7 +4425,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4632,6 +4635,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>142000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4674,7 +4680,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4884,6 +4890,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4893,7 +4902,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5103,6 +5112,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>181233.60689088883</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>191635.63229330175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5145,7 +5157,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5355,6 +5367,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5364,7 +5379,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5574,6 +5589,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>41233.606890888826</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>49635.632293301751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5595,11 +5613,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="418735232"/>
-        <c:axId val="432095616"/>
+        <c:axId val="78677504"/>
+        <c:axId val="78679424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="418735232"/>
+        <c:axId val="78677504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5642,14 +5660,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432095616"/>
+        <c:crossAx val="78679424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="432095616"/>
+        <c:axId val="78679424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5700,7 +5718,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="418735232"/>
+        <c:crossAx val="78677504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6106,7 +6124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB72"/>
+  <dimension ref="A1:AB73"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8537,6 +8555,35 @@
       </c>
       <c r="I72" s="17">
         <v>41233.606890888826</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="12.75">
+      <c r="A73" s="14">
+        <v>46022</v>
+      </c>
+      <c r="B73" s="15">
+        <v>5.0477412109374997</v>
+      </c>
+      <c r="C73" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D73" s="17">
+        <v>396.21682578860788</v>
+      </c>
+      <c r="E73" s="17">
+        <v>37964.630967622434</v>
+      </c>
+      <c r="F73" s="17">
+        <v>191635.63229330175</v>
+      </c>
+      <c r="G73" s="17">
+        <v>142000</v>
+      </c>
+      <c r="H73" s="17">
+        <v>191635.63229330175</v>
+      </c>
+      <c r="I73" s="17">
+        <v>49635.632293301751</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="924">
   <si>
     <t>PE</t>
   </si>
@@ -3631,6 +3631,78 @@
   </si>
   <si>
     <t xml:space="preserve">2025/11/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/28
 </t>
   </si>
 </sst>
@@ -5613,11 +5685,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78677504"/>
-        <c:axId val="78679424"/>
+        <c:axId val="162556928"/>
+        <c:axId val="162559488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78677504"/>
+        <c:axId val="162556928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5660,14 +5732,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78679424"/>
+        <c:crossAx val="162559488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="78679424"/>
+        <c:axId val="162559488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5718,7 +5790,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78677504"/>
+        <c:crossAx val="162556928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8599,7 +8671,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1154"/>
+  <dimension ref="A1:D1174"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26690,7 +26762,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1154" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1174" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27054,6 +27126,326 @@
       <c r="D1154" s="18">
         <f>SUM(C$3:C1154)/A1154</f>
         <v>25.866548769817285</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4">
+      <c r="A1155" s="18">
+        <f t="shared" si="7"/>
+        <v>1153</v>
+      </c>
+      <c r="B1155" s="30" t="s">
+        <v>906</v>
+      </c>
+      <c r="C1155" s="31">
+        <v>31.879999160766602</v>
+      </c>
+      <c r="D1155" s="18">
+        <f>SUM(C$3:C1155)/A1155</f>
+        <v>25.871764251509347</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4">
+      <c r="A1156" s="18">
+        <f t="shared" si="7"/>
+        <v>1154</v>
+      </c>
+      <c r="B1156" s="30" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1156" s="31">
+        <v>32.090000152587891</v>
+      </c>
+      <c r="D1156" s="18">
+        <f>SUM(C$3:C1156)/A1156</f>
+        <v>25.877152670834374</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4">
+      <c r="A1157" s="18">
+        <f t="shared" si="7"/>
+        <v>1155</v>
+      </c>
+      <c r="B1157" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="C1157" s="31">
+        <v>32.189998626708984</v>
+      </c>
+      <c r="D1157" s="18">
+        <f>SUM(C$3:C1157)/A1157</f>
+        <v>25.882618338328637</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4">
+      <c r="A1158" s="18">
+        <f t="shared" si="7"/>
+        <v>1156</v>
+      </c>
+      <c r="B1158" s="30" t="s">
+        <v>909</v>
+      </c>
+      <c r="C1158" s="31">
+        <v>31.979999542236328</v>
+      </c>
+      <c r="D1158" s="18">
+        <f>SUM(C$3:C1158)/A1158</f>
+        <v>25.887892889543089</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4">
+      <c r="A1159" s="18">
+        <f t="shared" si="7"/>
+        <v>1157</v>
+      </c>
+      <c r="B1159" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="C1159" s="31">
+        <v>32.330001831054687</v>
+      </c>
+      <c r="D1159" s="18">
+        <f>SUM(C$3:C1159)/A1159</f>
+        <v>25.893460831584154</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4">
+      <c r="A1160" s="18">
+        <f t="shared" si="7"/>
+        <v>1158</v>
+      </c>
+      <c r="B1160" s="30" t="s">
+        <v>911</v>
+      </c>
+      <c r="C1160" s="31">
+        <v>32.669998168945313</v>
+      </c>
+      <c r="D1160" s="18">
+        <f>SUM(C$3:C1160)/A1160</f>
+        <v>25.899312763654414</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4">
+      <c r="A1161" s="18">
+        <f t="shared" si="7"/>
+        <v>1159</v>
+      </c>
+      <c r="B1161" s="30" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1161" s="31">
+        <v>32.029998779296875</v>
+      </c>
+      <c r="D1161" s="18">
+        <f>SUM(C$3:C1161)/A1161</f>
+        <v>25.904602397835298</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4">
+      <c r="A1162" s="18">
+        <f t="shared" si="7"/>
+        <v>1160</v>
+      </c>
+      <c r="B1162" s="30" t="s">
+        <v>913</v>
+      </c>
+      <c r="C1162" s="31">
+        <v>32.090000152587891</v>
+      </c>
+      <c r="D1162" s="18">
+        <f>SUM(C$3:C1162)/A1162</f>
+        <v>25.909934637279051</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4">
+      <c r="A1163" s="18">
+        <f t="shared" si="7"/>
+        <v>1161</v>
+      </c>
+      <c r="B1163" s="30" t="s">
+        <v>914</v>
+      </c>
+      <c r="C1163" s="31">
+        <v>32.299999237060547</v>
+      </c>
+      <c r="D1163" s="18">
+        <f>SUM(C$3:C1163)/A1163</f>
+        <v>25.915438568889542</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4">
+      <c r="A1164" s="18">
+        <f t="shared" si="7"/>
+        <v>1162</v>
+      </c>
+      <c r="B1164" s="30" t="s">
+        <v>915</v>
+      </c>
+      <c r="C1164" s="31">
+        <v>32.520000457763672</v>
+      </c>
+      <c r="D1164" s="18">
+        <f>SUM(C$3:C1164)/A1164</f>
+        <v>25.921122357089949</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4">
+      <c r="A1165" s="18">
+        <f t="shared" si="7"/>
+        <v>1163</v>
+      </c>
+      <c r="B1165" s="30" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1165" s="31">
+        <v>32.470001220703125</v>
+      </c>
+      <c r="D1165" s="18">
+        <f>SUM(C$3:C1165)/A1165</f>
+        <v>25.926753379328655</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4">
+      <c r="A1166" s="18">
+        <f t="shared" si="7"/>
+        <v>1164</v>
+      </c>
+      <c r="B1166" s="30" t="s">
+        <v>917</v>
+      </c>
+      <c r="C1166" s="31">
+        <v>31.969999313354492</v>
+      </c>
+      <c r="D1166" s="18">
+        <f>SUM(C$3:C1166)/A1166</f>
+        <v>25.931945171368195</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4">
+      <c r="A1167" s="18">
+        <f t="shared" si="7"/>
+        <v>1165</v>
+      </c>
+      <c r="B1167" s="30" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1167" s="31">
+        <v>32.180000305175781</v>
+      </c>
+      <c r="D1167" s="18">
+        <f>SUM(C$3:C1167)/A1167</f>
+        <v>25.937308308822107</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4">
+      <c r="A1168" s="18">
+        <f t="shared" si="7"/>
+        <v>1166</v>
+      </c>
+      <c r="B1168" s="30" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1168" s="31">
+        <v>32.25</v>
+      </c>
+      <c r="D1168" s="18">
+        <f>SUM(C$3:C1168)/A1168</f>
+        <v>25.942722281112996</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4">
+      <c r="A1169" s="18">
+        <f t="shared" si="7"/>
+        <v>1167</v>
+      </c>
+      <c r="B1169" s="30" t="s">
+        <v>920</v>
+      </c>
+      <c r="C1169" s="31">
+        <v>32.389999389648438</v>
+      </c>
+      <c r="D1169" s="18">
+        <f>SUM(C$3:C1169)/A1169</f>
+        <v>25.948246940160587</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4">
+      <c r="A1170" s="18">
+        <f t="shared" si="7"/>
+        <v>1168</v>
+      </c>
+      <c r="B1170" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1170" s="31">
+        <v>31.930000305175781</v>
+      </c>
+      <c r="D1170" s="18">
+        <f>SUM(C$3:C1170)/A1170</f>
+        <v>25.953368304342963</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4">
+      <c r="A1171" s="18">
+        <f t="shared" si="7"/>
+        <v>1169</v>
+      </c>
+      <c r="B1171" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="C1171" s="31">
+        <v>32.029998779296875</v>
+      </c>
+      <c r="D1171" s="18">
+        <f>SUM(C$3:C1171)/A1171</f>
+        <v>25.958566448461827</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4">
+      <c r="A1172" s="18">
+        <f t="shared" si="7"/>
+        <v>1170</v>
+      </c>
+      <c r="B1172" s="30" t="s">
+        <v>923</v>
+      </c>
+      <c r="C1172" s="31">
+        <v>31.959999084472656</v>
+      </c>
+      <c r="D1172" s="18">
+        <f>SUM(C$3:C1172)/A1172</f>
+        <v>25.963695878065256</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4">
+      <c r="A1173" s="18">
+        <f t="shared" si="7"/>
+        <v>1171</v>
+      </c>
+      <c r="B1173" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C1173" s="31">
+        <v>31.540000915527344</v>
+      </c>
+      <c r="D1173" s="18">
+        <f>SUM(C$3:C1173)/A1173</f>
+        <v>25.968457880659159</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4">
+      <c r="A1174" s="18">
+        <f t="shared" si="7"/>
+        <v>1172</v>
+      </c>
+      <c r="B1174" s="30">
+        <v>46052</v>
+      </c>
+      <c r="C1174" s="31">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D1174" s="18">
+        <f>SUM(C$3:C1174)/A1174</f>
+        <v>25.973356806597167</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -4275,7 +4275,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4488,6 +4488,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4497,7 +4500,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4710,6 +4713,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>144000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4752,7 +4758,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4965,6 +4971,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4974,7 +4983,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5187,6 +5196,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>191635.63229330175</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>198435.56287226095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5229,7 +5241,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5442,6 +5454,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5451,7 +5466,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5664,6 +5679,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>49635.632293301751</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>54435.562872260954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,11 +5703,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="162556928"/>
-        <c:axId val="162559488"/>
+        <c:axId val="89504000"/>
+        <c:axId val="104017280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="162556928"/>
+        <c:axId val="89504000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5732,14 +5750,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162559488"/>
+        <c:crossAx val="104017280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="162559488"/>
+        <c:axId val="104017280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5790,7 +5808,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162556928"/>
+        <c:crossAx val="89504000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6196,7 +6214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB73"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8656,6 +8674,35 @@
       </c>
       <c r="I73" s="17">
         <v>49635.632293301751</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="12.75">
+      <c r="A74" s="14">
+        <v>46052</v>
+      </c>
+      <c r="B74" s="15">
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="C74" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D74" s="17">
+        <v>386.53521198002471</v>
+      </c>
+      <c r="E74" s="17">
+        <v>38351.166179602456</v>
+      </c>
+      <c r="F74" s="17">
+        <v>198435.56287226095</v>
+      </c>
+      <c r="G74" s="17">
+        <v>144000</v>
+      </c>
+      <c r="H74" s="17">
+        <v>198435.56287226095</v>
+      </c>
+      <c r="I74" s="17">
+        <v>54435.562872260954</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="936">
   <si>
     <t>PE</t>
   </si>
@@ -3703,6 +3703,54 @@
   </si>
   <si>
     <t xml:space="preserve">2026/1/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/25
 </t>
   </si>
 </sst>
@@ -5703,11 +5751,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="89504000"/>
-        <c:axId val="104017280"/>
+        <c:axId val="383488384"/>
+        <c:axId val="383489920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="89504000"/>
+        <c:axId val="383488384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5750,14 +5798,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="104017280"/>
+        <c:crossAx val="383489920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="104017280"/>
+        <c:axId val="383489920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5808,7 +5856,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89504000"/>
+        <c:crossAx val="383488384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8718,7 +8766,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1174"/>
+  <dimension ref="A1:D1188"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26809,7 +26857,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1174" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1188" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27493,6 +27541,230 @@
       <c r="D1174" s="18">
         <f>SUM(C$3:C1174)/A1174</f>
         <v>25.973356806597167</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4">
+      <c r="A1175" s="18">
+        <f t="shared" si="7"/>
+        <v>1173</v>
+      </c>
+      <c r="B1175" s="30" t="s">
+        <v>924</v>
+      </c>
+      <c r="C1175" s="31">
+        <v>30.950000760000002</v>
+      </c>
+      <c r="D1175" s="18">
+        <f>SUM(C$3:C1175)/A1175</f>
+        <v>25.977599469814049</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4">
+      <c r="A1176" s="18">
+        <f t="shared" si="7"/>
+        <v>1174</v>
+      </c>
+      <c r="B1176" s="30" t="s">
+        <v>925</v>
+      </c>
+      <c r="C1176" s="31">
+        <v>31.409999849999998</v>
+      </c>
+      <c r="D1176" s="18">
+        <f>SUM(C$3:C1176)/A1176</f>
+        <v>25.982226727378087</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4">
+      <c r="A1177" s="18">
+        <f t="shared" si="7"/>
+        <v>1175</v>
+      </c>
+      <c r="B1177" s="30" t="s">
+        <v>926</v>
+      </c>
+      <c r="C1177" s="31">
+        <v>31.579999919999999</v>
+      </c>
+      <c r="D1177" s="18">
+        <f>SUM(C$3:C1177)/A1177</f>
+        <v>25.986990789669679</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4">
+      <c r="A1178" s="18">
+        <f t="shared" si="7"/>
+        <v>1176</v>
+      </c>
+      <c r="B1178" s="30" t="s">
+        <v>927</v>
+      </c>
+      <c r="C1178" s="31">
+        <v>31.229999540000001</v>
+      </c>
+      <c r="D1178" s="18">
+        <f>SUM(C$3:C1178)/A1178</f>
+        <v>25.991449130443769</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4">
+      <c r="A1179" s="18">
+        <f t="shared" si="7"/>
+        <v>1177</v>
+      </c>
+      <c r="B1179" s="30" t="s">
+        <v>928</v>
+      </c>
+      <c r="C1179" s="31">
+        <v>31.219999309999999</v>
+      </c>
+      <c r="D1179" s="18">
+        <f>SUM(C$3:C1179)/A1179</f>
+        <v>25.995891399075511</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4">
+      <c r="A1180" s="18">
+        <f t="shared" si="7"/>
+        <v>1178</v>
+      </c>
+      <c r="B1180" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="C1180" s="31">
+        <v>31.729999540000001</v>
+      </c>
+      <c r="D1180" s="18">
+        <f>SUM(C$3:C1180)/A1180</f>
+        <v>26.000759063032152</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4">
+      <c r="A1181" s="18">
+        <f t="shared" si="7"/>
+        <v>1179</v>
+      </c>
+      <c r="B1181" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="C1181" s="31">
+        <v>31.760000229999999</v>
+      </c>
+      <c r="D1181" s="18">
+        <f>SUM(C$3:C1181)/A1181</f>
+        <v>26.005643915591069</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4">
+      <c r="A1182" s="18">
+        <f t="shared" si="7"/>
+        <v>1180</v>
+      </c>
+      <c r="B1182" s="30" t="s">
+        <v>931</v>
+      </c>
+      <c r="C1182" s="31">
+        <v>31.590000150000002</v>
+      </c>
+      <c r="D1182" s="18">
+        <f>SUM(C$3:C1182)/A1182</f>
+        <v>26.010376420874469</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4">
+      <c r="A1183" s="18">
+        <f t="shared" si="7"/>
+        <v>1181</v>
+      </c>
+      <c r="B1183" s="30" t="s">
+        <v>932</v>
+      </c>
+      <c r="C1183" s="31">
+        <v>32</v>
+      </c>
+      <c r="D1183" s="18">
+        <f>SUM(C$3:C1183)/A1183</f>
+        <v>26.015448075048155</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4">
+      <c r="A1184" s="18">
+        <f t="shared" si="7"/>
+        <v>1182</v>
+      </c>
+      <c r="B1184" s="30" t="s">
+        <v>933</v>
+      </c>
+      <c r="C1184" s="31">
+        <v>31.590000150000002</v>
+      </c>
+      <c r="D1184" s="18">
+        <f>SUM(C$3:C1184)/A1184</f>
+        <v>26.020164278157253</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4">
+      <c r="A1185" s="18">
+        <f t="shared" si="7"/>
+        <v>1183</v>
+      </c>
+      <c r="B1185" s="30" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1185" s="31">
+        <v>31.829999919999999</v>
+      </c>
+      <c r="D1185" s="18">
+        <f>SUM(C$3:C1185)/A1185</f>
+        <v>26.025075381827449</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4">
+      <c r="A1186" s="18">
+        <f t="shared" si="7"/>
+        <v>1184</v>
+      </c>
+      <c r="B1186" s="30" t="s">
+        <v>935</v>
+      </c>
+      <c r="C1186" s="31">
+        <v>32.090000150000002</v>
+      </c>
+      <c r="D1186" s="18">
+        <f>SUM(C$3:C1186)/A1186</f>
+        <v>26.030197784503272</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4">
+      <c r="A1187" s="18">
+        <f t="shared" si="7"/>
+        <v>1185</v>
+      </c>
+      <c r="B1187" s="30">
+        <v>46079</v>
+      </c>
+      <c r="C1187" s="31">
+        <v>31.920000080000001</v>
+      </c>
+      <c r="D1187" s="18">
+        <f>SUM(C$3:C1187)/A1187</f>
+        <v>26.03516808179905</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4">
+      <c r="A1188" s="18">
+        <f t="shared" si="7"/>
+        <v>1186</v>
+      </c>
+      <c r="B1188" s="30">
+        <v>46080</v>
+      </c>
+      <c r="C1188" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D1188" s="18">
+        <f>SUM(C$3:C1188)/A1188</f>
+        <v>26.039818023753689</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -4323,7 +4323,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4539,6 +4539,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4548,7 +4551,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4764,6 +4767,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>144000</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>146000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4806,7 +4812,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5022,6 +5028,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5031,7 +5040,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5247,6 +5256,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>198435.56287226095</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>198359.00077810945</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5289,7 +5301,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5505,6 +5517,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5514,7 +5529,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5730,6 +5745,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>54435.562872260954</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>52359.000778109446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5751,11 +5769,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="383488384"/>
-        <c:axId val="383489920"/>
+        <c:axId val="79177216"/>
+        <c:axId val="79178752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="383488384"/>
+        <c:axId val="79177216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5798,14 +5816,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="383489920"/>
+        <c:crossAx val="79178752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="383489920"/>
+        <c:axId val="79178752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5856,7 +5874,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="383488384"/>
+        <c:crossAx val="79177216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6262,7 +6280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB74"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8751,6 +8769,35 @@
       </c>
       <c r="I74" s="17">
         <v>54435.562872260954</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="12.75">
+      <c r="A75" s="14">
+        <v>46080</v>
+      </c>
+      <c r="B75" s="15">
+        <v>5.1200268554687502</v>
+      </c>
+      <c r="C75" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D75" s="17">
+        <v>390.62295110108272</v>
+      </c>
+      <c r="E75" s="17">
+        <v>38741.789130703539</v>
+      </c>
+      <c r="F75" s="17">
+        <v>198359.00077810945</v>
+      </c>
+      <c r="G75" s="17">
+        <v>146000</v>
+      </c>
+      <c r="H75" s="17">
+        <v>198359.00077810945</v>
+      </c>
+      <c r="I75" s="17">
+        <v>52359.000778109446</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="956">
   <si>
     <t>PE</t>
   </si>
@@ -3751,6 +3751,86 @@
   </si>
   <si>
     <t xml:space="preserve">2026/2/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/27
 </t>
   </si>
 </sst>
@@ -5769,11 +5849,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79177216"/>
-        <c:axId val="79178752"/>
+        <c:axId val="329934336"/>
+        <c:axId val="329936256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79177216"/>
+        <c:axId val="329934336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5816,14 +5896,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79178752"/>
+        <c:crossAx val="329936256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79178752"/>
+        <c:axId val="329936256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5874,7 +5954,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79177216"/>
+        <c:crossAx val="329934336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8813,7 +8893,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1188"/>
+  <dimension ref="A1:D1210"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26904,7 +26984,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1188" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1210" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27812,6 +27892,358 @@
       <c r="D1188" s="18">
         <f>SUM(C$3:C1188)/A1188</f>
         <v>26.039818023753689</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4">
+      <c r="A1189" s="18">
+        <f t="shared" si="7"/>
+        <v>1187</v>
+      </c>
+      <c r="B1189" s="30" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1189" s="31">
+        <v>31.690000529999999</v>
+      </c>
+      <c r="D1189" s="18">
+        <f>SUM(C$3:C1189)/A1189</f>
+        <v>26.044578076412702</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4">
+      <c r="A1190" s="18">
+        <f t="shared" si="7"/>
+        <v>1188</v>
+      </c>
+      <c r="B1190" s="30" t="s">
+        <v>937</v>
+      </c>
+      <c r="C1190" s="31">
+        <v>30.899999619999999</v>
+      </c>
+      <c r="D1190" s="18">
+        <f>SUM(C$3:C1190)/A1190</f>
+        <v>26.048665131584073</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4">
+      <c r="A1191" s="18">
+        <f t="shared" si="7"/>
+        <v>1189</v>
+      </c>
+      <c r="B1191" s="30" t="s">
+        <v>938</v>
+      </c>
+      <c r="C1191" s="31">
+        <v>30.629999160000001</v>
+      </c>
+      <c r="D1191" s="18">
+        <f>SUM(C$3:C1191)/A1191</f>
+        <v>26.052518230009987</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4">
+      <c r="A1192" s="18">
+        <f t="shared" si="7"/>
+        <v>1190</v>
+      </c>
+      <c r="B1192" s="30" t="s">
+        <v>939</v>
+      </c>
+      <c r="C1192" s="31">
+        <v>31.059999470000001</v>
+      </c>
+      <c r="D1192" s="18">
+        <f>SUM(C$3:C1192)/A1192</f>
+        <v>26.05672619743855</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4">
+      <c r="A1193" s="18">
+        <f t="shared" si="7"/>
+        <v>1191</v>
+      </c>
+      <c r="B1193" s="30" t="s">
+        <v>940</v>
+      </c>
+      <c r="C1193" s="31">
+        <v>31.170000080000001</v>
+      </c>
+      <c r="D1193" s="18">
+        <f>SUM(C$3:C1193)/A1193</f>
+        <v>26.061019458465051</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4">
+      <c r="A1194" s="18">
+        <f t="shared" si="7"/>
+        <v>1192</v>
+      </c>
+      <c r="B1194" s="30" t="s">
+        <v>941</v>
+      </c>
+      <c r="C1194" s="31">
+        <v>30.950000760000002</v>
+      </c>
+      <c r="D1194" s="18">
+        <f>SUM(C$3:C1194)/A1194</f>
+        <v>26.065120952845533</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4">
+      <c r="A1195" s="18">
+        <f t="shared" si="7"/>
+        <v>1193</v>
+      </c>
+      <c r="B1195" s="30" t="s">
+        <v>942</v>
+      </c>
+      <c r="C1195" s="31">
+        <v>30.950000760000002</v>
+      </c>
+      <c r="D1195" s="18">
+        <f>SUM(C$3:C1195)/A1195</f>
+        <v>26.069215571292435</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4">
+      <c r="A1196" s="18">
+        <f t="shared" si="7"/>
+        <v>1194</v>
+      </c>
+      <c r="B1196" s="30" t="s">
+        <v>943</v>
+      </c>
+      <c r="C1196" s="31">
+        <v>32.36000061</v>
+      </c>
+      <c r="D1196" s="18">
+        <f>SUM(C$3:C1196)/A1196</f>
+        <v>26.074484235478955</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4">
+      <c r="A1197" s="18">
+        <f t="shared" si="7"/>
+        <v>1195</v>
+      </c>
+      <c r="B1197" s="30" t="s">
+        <v>944</v>
+      </c>
+      <c r="C1197" s="31">
+        <v>32.150001529999997</v>
+      </c>
+      <c r="D1197" s="18">
+        <f>SUM(C$3:C1197)/A1197</f>
+        <v>26.079568350369769</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4">
+      <c r="A1198" s="18">
+        <f t="shared" si="7"/>
+        <v>1196</v>
+      </c>
+      <c r="B1198" s="30" t="s">
+        <v>945</v>
+      </c>
+      <c r="C1198" s="31">
+        <v>31.950000760000002</v>
+      </c>
+      <c r="D1198" s="18">
+        <f>SUM(C$3:C1198)/A1198</f>
+        <v>26.084476738672137</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4">
+      <c r="A1199" s="18">
+        <f t="shared" si="7"/>
+        <v>1197</v>
+      </c>
+      <c r="B1199" s="30" t="s">
+        <v>946</v>
+      </c>
+      <c r="C1199" s="31">
+        <v>32.25</v>
+      </c>
+      <c r="D1199" s="18">
+        <f>SUM(C$3:C1199)/A1199</f>
+        <v>26.089627551755953</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4">
+      <c r="A1200" s="18">
+        <f t="shared" si="7"/>
+        <v>1198</v>
+      </c>
+      <c r="B1200" s="30" t="s">
+        <v>947</v>
+      </c>
+      <c r="C1200" s="31">
+        <v>31.719999309999999</v>
+      </c>
+      <c r="D1200" s="18">
+        <f>SUM(C$3:C1200)/A1200</f>
+        <v>26.094327361236957</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4">
+      <c r="A1201" s="18">
+        <f t="shared" si="7"/>
+        <v>1199</v>
+      </c>
+      <c r="B1201" s="30" t="s">
+        <v>948</v>
+      </c>
+      <c r="C1201" s="31">
+        <v>32.060001370000002</v>
+      </c>
+      <c r="D1201" s="18">
+        <f>SUM(C$3:C1201)/A1201</f>
+        <v>26.09930290252867</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4">
+      <c r="A1202" s="18">
+        <f t="shared" si="7"/>
+        <v>1200</v>
+      </c>
+      <c r="B1202" s="30" t="s">
+        <v>949</v>
+      </c>
+      <c r="C1202" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D1202" s="18">
+        <f>SUM(C$3:C1202)/A1202</f>
+        <v>26.103845149476562</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4">
+      <c r="A1203" s="18">
+        <f t="shared" si="7"/>
+        <v>1201</v>
+      </c>
+      <c r="B1203" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="C1203" s="31">
+        <v>31.729999540000001</v>
+      </c>
+      <c r="D1203" s="18">
+        <f>SUM(C$3:C1203)/A1203</f>
+        <v>26.108529707670169</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4">
+      <c r="A1204" s="18">
+        <f t="shared" si="7"/>
+        <v>1202</v>
+      </c>
+      <c r="B1204" s="30" t="s">
+        <v>951</v>
+      </c>
+      <c r="C1204" s="31">
+        <v>30.75</v>
+      </c>
+      <c r="D1204" s="18">
+        <f>SUM(C$3:C1204)/A1204</f>
+        <v>26.112391163820195</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4">
+      <c r="A1205" s="18">
+        <f t="shared" si="7"/>
+        <v>1203</v>
+      </c>
+      <c r="B1205" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="C1205" s="31">
+        <v>30.870000839999999</v>
+      </c>
+      <c r="D1205" s="18">
+        <f>SUM(C$3:C1205)/A1205</f>
+        <v>26.116345951580943</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4">
+      <c r="A1206" s="18">
+        <f t="shared" si="7"/>
+        <v>1204</v>
+      </c>
+      <c r="B1206" s="30" t="s">
+        <v>953</v>
+      </c>
+      <c r="C1206" s="31">
+        <v>31.38999939</v>
+      </c>
+      <c r="D1206" s="18">
+        <f>SUM(C$3:C1206)/A1206</f>
+        <v>26.120726062410196</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4">
+      <c r="A1207" s="18">
+        <f t="shared" si="7"/>
+        <v>1205</v>
+      </c>
+      <c r="B1207" s="30" t="s">
+        <v>954</v>
+      </c>
+      <c r="C1207" s="31">
+        <v>30.969999309999999</v>
+      </c>
+      <c r="D1207" s="18">
+        <f>SUM(C$3:C1207)/A1207</f>
+        <v>26.124750355561723</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4">
+      <c r="A1208" s="18">
+        <f t="shared" si="7"/>
+        <v>1206</v>
+      </c>
+      <c r="B1208" s="30" t="s">
+        <v>955</v>
+      </c>
+      <c r="C1208" s="31">
+        <v>31.299999239999998</v>
+      </c>
+      <c r="D1208" s="18">
+        <f>SUM(C$3:C1208)/A1208</f>
+        <v>26.129041606709681</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4">
+      <c r="A1209" s="18">
+        <f t="shared" si="7"/>
+        <v>1207</v>
+      </c>
+      <c r="B1209" s="30">
+        <v>46111</v>
+      </c>
+      <c r="C1209" s="31">
+        <v>31.299999239999998</v>
+      </c>
+      <c r="D1209" s="18">
+        <f>SUM(C$3:C1209)/A1209</f>
+        <v>26.133325747250932</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4">
+      <c r="A1210" s="18">
+        <f t="shared" si="7"/>
+        <v>1208</v>
+      </c>
+      <c r="B1210" s="30">
+        <v>46112</v>
+      </c>
+      <c r="C1210" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D1210" s="18">
+        <f>SUM(C$3:C1210)/A1210</f>
+        <v>26.136981933917117</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -4403,7 +4403,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4622,6 +4622,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4631,7 +4634,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4850,6 +4853,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>146000</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>148000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4892,7 +4898,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5111,6 +5117,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5120,7 +5129,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5339,6 +5348,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>198359.00077810945</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>191259.80680937381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5381,7 +5393,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5600,6 +5612,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5609,7 +5624,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5828,6 +5843,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>52359.000778109446</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>43259.806809373811</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5849,11 +5867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="329934336"/>
-        <c:axId val="329936256"/>
+        <c:axId val="92162688"/>
+        <c:axId val="367295872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="329934336"/>
+        <c:axId val="92162688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5896,14 +5914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="329936256"/>
+        <c:crossAx val="367295872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="329936256"/>
+        <c:axId val="367295872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5972,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="329934336"/>
+        <c:crossAx val="92162688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6360,7 +6378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB76"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8878,6 +8896,35 @@
       </c>
       <c r="I75" s="17">
         <v>52359.000778109446</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="12.75">
+      <c r="A76" s="14">
+        <v>46112</v>
+      </c>
+      <c r="B76" s="15">
+        <v>4.8851591796875002</v>
+      </c>
+      <c r="C76" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D76" s="17">
+        <v>409.40324080247029</v>
+      </c>
+      <c r="E76" s="17">
+        <v>39151.192371506011</v>
+      </c>
+      <c r="F76" s="17">
+        <v>191259.80680937381</v>
+      </c>
+      <c r="G76" s="17">
+        <v>148000</v>
+      </c>
+      <c r="H76" s="17">
+        <v>191259.80680937381</v>
+      </c>
+      <c r="I76" s="17">
+        <v>43259.806809373811</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="975">
   <si>
     <t>PE</t>
   </si>
@@ -3831,6 +3831,82 @@
   </si>
   <si>
     <t xml:space="preserve">2026/3/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/23
 </t>
   </si>
 </sst>
@@ -5867,11 +5943,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92162688"/>
-        <c:axId val="367295872"/>
+        <c:axId val="344213376"/>
+        <c:axId val="431454848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92162688"/>
+        <c:axId val="344213376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5914,14 +5990,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="367295872"/>
+        <c:crossAx val="431454848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="367295872"/>
+        <c:axId val="431454848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5972,7 +6048,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92162688"/>
+        <c:crossAx val="344213376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8940,7 +9016,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1210"/>
+  <dimension ref="A1:D1231"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -27031,7 +27107,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1210" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1226" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -28291,6 +28367,342 @@
       <c r="D1210" s="18">
         <f>SUM(C$3:C1210)/A1210</f>
         <v>26.136981933917117</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4">
+      <c r="A1211" s="18">
+        <f t="shared" si="7"/>
+        <v>1209</v>
+      </c>
+      <c r="B1211" s="30" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1211" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D1211" s="18">
+        <f>SUM(C$3:C1211)/A1211</f>
+        <v>26.140632072300974</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4">
+      <c r="A1212" s="18">
+        <f t="shared" si="7"/>
+        <v>1210</v>
+      </c>
+      <c r="B1212" s="30" t="s">
+        <v>957</v>
+      </c>
+      <c r="C1212" s="31">
+        <v>30.340000150000002</v>
+      </c>
+      <c r="D1212" s="18">
+        <f>SUM(C$3:C1212)/A1212</f>
+        <v>26.144102624431305</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4">
+      <c r="A1213" s="18">
+        <f t="shared" si="7"/>
+        <v>1211</v>
+      </c>
+      <c r="B1213" s="30" t="s">
+        <v>958</v>
+      </c>
+      <c r="C1213" s="31">
+        <v>29.940000529999999</v>
+      </c>
+      <c r="D1213" s="18">
+        <f>SUM(C$3:C1213)/A1213</f>
+        <v>26.147237139629958</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4">
+      <c r="A1214" s="18">
+        <f t="shared" si="7"/>
+        <v>1212</v>
+      </c>
+      <c r="B1214" s="30" t="s">
+        <v>959</v>
+      </c>
+      <c r="C1214" s="31">
+        <v>29.979999540000001</v>
+      </c>
+      <c r="D1214" s="18">
+        <f>SUM(C$3:C1214)/A1214</f>
+        <v>26.150399484844783</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4">
+      <c r="A1215" s="18">
+        <f t="shared" si="7"/>
+        <v>1213</v>
+      </c>
+      <c r="B1215" s="30" t="s">
+        <v>960</v>
+      </c>
+      <c r="C1215" s="31">
+        <v>31.379999160000001</v>
+      </c>
+      <c r="D1215" s="18">
+        <f>SUM(C$3:C1215)/A1215</f>
+        <v>26.154710778888603</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4">
+      <c r="A1216" s="18">
+        <f t="shared" si="7"/>
+        <v>1214</v>
+      </c>
+      <c r="B1216" s="30" t="s">
+        <v>961</v>
+      </c>
+      <c r="C1216" s="31">
+        <v>31.299999239999998</v>
+      </c>
+      <c r="D1216" s="18">
+        <f>SUM(C$3:C1216)/A1216</f>
+        <v>26.158949072513902</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4">
+      <c r="A1217" s="18">
+        <f t="shared" si="7"/>
+        <v>1215</v>
+      </c>
+      <c r="B1217" s="30" t="s">
+        <v>962</v>
+      </c>
+      <c r="C1217" s="31">
+        <v>32.38999939</v>
+      </c>
+      <c r="D1217" s="18">
+        <f>SUM(C$3:C1217)/A1217</f>
+        <v>26.164077508989202</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4">
+      <c r="A1218" s="18">
+        <f t="shared" si="7"/>
+        <v>1216</v>
+      </c>
+      <c r="B1218" s="30" t="s">
+        <v>963</v>
+      </c>
+      <c r="C1218" s="31">
+        <v>32.72000122</v>
+      </c>
+      <c r="D1218" s="18">
+        <f>SUM(C$3:C1218)/A1218</f>
+        <v>26.169468893619968</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4">
+      <c r="A1219" s="18">
+        <f t="shared" si="7"/>
+        <v>1217</v>
+      </c>
+      <c r="B1219" s="30" t="s">
+        <v>964</v>
+      </c>
+      <c r="C1219" s="31">
+        <v>33.349998470000003</v>
+      </c>
+      <c r="D1219" s="18">
+        <f>SUM(C$3:C1219)/A1219</f>
+        <v>26.175369082261199</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4">
+      <c r="A1220" s="18">
+        <f t="shared" si="7"/>
+        <v>1218</v>
+      </c>
+      <c r="B1220" s="30" t="s">
+        <v>965</v>
+      </c>
+      <c r="C1220" s="31">
+        <v>33.060001370000002</v>
+      </c>
+      <c r="D1220" s="18">
+        <f>SUM(C$3:C1220)/A1220</f>
+        <v>26.181021489722394</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4">
+      <c r="A1221" s="18">
+        <f t="shared" si="7"/>
+        <v>1219</v>
+      </c>
+      <c r="B1221" s="30" t="s">
+        <v>966</v>
+      </c>
+      <c r="C1221" s="31">
+        <v>33.799999239999998</v>
+      </c>
+      <c r="D1221" s="18">
+        <f>SUM(C$3:C1221)/A1221</f>
+        <v>26.187271676556094</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4">
+      <c r="A1222" s="18">
+        <f t="shared" si="7"/>
+        <v>1220</v>
+      </c>
+      <c r="B1222" s="30" t="s">
+        <v>967</v>
+      </c>
+      <c r="C1222" s="31">
+        <v>33.91999817</v>
+      </c>
+      <c r="D1222" s="18">
+        <f>SUM(C$3:C1222)/A1222</f>
+        <v>26.193609976960555</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4">
+      <c r="A1223" s="18">
+        <f t="shared" si="7"/>
+        <v>1221</v>
+      </c>
+      <c r="B1223" s="30" t="s">
+        <v>968</v>
+      </c>
+      <c r="C1223" s="31">
+        <v>34.040000919999997</v>
+      </c>
+      <c r="D1223" s="18">
+        <f>SUM(C$3:C1223)/A1223</f>
+        <v>26.200036177569103</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4">
+      <c r="A1224" s="18">
+        <f t="shared" si="7"/>
+        <v>1222</v>
+      </c>
+      <c r="B1224" s="30" t="s">
+        <v>969</v>
+      </c>
+      <c r="C1224" s="31">
+        <v>34.159999849999998</v>
+      </c>
+      <c r="D1224" s="18">
+        <f>SUM(C$3:C1224)/A1224</f>
+        <v>26.206550059461435</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4">
+      <c r="A1225" s="18">
+        <f t="shared" si="7"/>
+        <v>1223</v>
+      </c>
+      <c r="B1225" s="30" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1225" s="31">
+        <v>34.380001069999999</v>
+      </c>
+      <c r="D1225" s="18">
+        <f>SUM(C$3:C1225)/A1225</f>
+        <v>26.213233175577983</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4">
+      <c r="A1226" s="18">
+        <f t="shared" si="7"/>
+        <v>1224</v>
+      </c>
+      <c r="B1226" s="30" t="s">
+        <v>974</v>
+      </c>
+      <c r="C1226" s="31">
+        <v>34.32</v>
+      </c>
+      <c r="D1226" s="18">
+        <f>SUM(C$3:C1226)/A1226</f>
+        <v>26.219856351088133</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4">
+      <c r="A1227" s="18">
+        <f t="shared" ref="A1227:A1231" si="8">A1226+1</f>
+        <v>1225</v>
+      </c>
+      <c r="B1227" s="30" t="s">
+        <v>971</v>
+      </c>
+      <c r="C1227" s="31">
+        <v>34.25</v>
+      </c>
+      <c r="D1227" s="18">
+        <f>SUM(C$3:C1227)/A1227</f>
+        <v>26.226411570393367</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4">
+      <c r="A1228" s="18">
+        <f t="shared" si="8"/>
+        <v>1226</v>
+      </c>
+      <c r="B1228" s="30" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1228" s="31">
+        <v>34.270000459999999</v>
+      </c>
+      <c r="D1228" s="18">
+        <f>SUM(C$3:C1228)/A1228</f>
+        <v>26.232972409618167</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4">
+      <c r="A1229" s="18">
+        <f t="shared" si="8"/>
+        <v>1227</v>
+      </c>
+      <c r="B1229" s="30" t="s">
+        <v>973</v>
+      </c>
+      <c r="C1229" s="31">
+        <v>33.75</v>
+      </c>
+      <c r="D1229" s="18">
+        <f>SUM(C$3:C1229)/A1229</f>
+        <v>26.239098756472597</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4">
+      <c r="A1230" s="18">
+        <f t="shared" si="8"/>
+        <v>1228</v>
+      </c>
+      <c r="B1230" s="30">
+        <v>46141</v>
+      </c>
+      <c r="C1230" s="31">
+        <v>34.459999080000003</v>
+      </c>
+      <c r="D1230" s="18">
+        <f>SUM(C$3:C1230)/A1230</f>
+        <v>26.245793300709998</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4">
+      <c r="A1231" s="18">
+        <f t="shared" si="8"/>
+        <v>1229</v>
+      </c>
+      <c r="B1231" s="30">
+        <v>46142</v>
+      </c>
+      <c r="C1231" s="31">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D1231" s="18">
+        <f>SUM(C$3:C1231)/A1231</f>
+        <v>26.252550181051159</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -4479,7 +4479,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4701,6 +4701,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4710,7 +4713,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4932,6 +4935,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>148000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>150000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4974,7 +4980,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5196,6 +5202,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5205,7 +5214,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5427,6 +5436,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>191259.80680937381</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>219124.99999266435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5469,7 +5481,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5691,6 +5703,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5700,7 +5715,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5922,6 +5937,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>43259.806809373811</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>69124.99999266435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5943,11 +5961,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="344213376"/>
-        <c:axId val="431454848"/>
+        <c:axId val="409984384"/>
+        <c:axId val="457925760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="344213376"/>
+        <c:axId val="409984384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5990,14 +6008,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431454848"/>
+        <c:crossAx val="457925760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="431454848"/>
+        <c:axId val="457925760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6048,7 +6066,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344213376"/>
+        <c:crossAx val="409984384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6454,7 +6472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB76"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9001,6 +9019,35 @@
       </c>
       <c r="I76" s="17">
         <v>43259.806809373811</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="12.75">
+      <c r="A77" s="14">
+        <v>46142</v>
+      </c>
+      <c r="B77" s="15">
+        <v>5.5458081054687502</v>
+      </c>
+      <c r="C77" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D77" s="17">
+        <v>360.63274494257917</v>
+      </c>
+      <c r="E77" s="17">
+        <v>39511.825116448592</v>
+      </c>
+      <c r="F77" s="17">
+        <v>219124.99999266435</v>
+      </c>
+      <c r="G77" s="17">
+        <v>150000</v>
+      </c>
+      <c r="H77" s="17">
+        <v>219124.99999266435</v>
+      </c>
+      <c r="I77" s="17">
+        <v>69124.99999266435</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="991">
   <si>
     <t>PE</t>
   </si>
@@ -3907,6 +3907,70 @@
   </si>
   <si>
     <t xml:space="preserve">2026/4/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/27
 </t>
   </si>
 </sst>
@@ -5961,11 +6025,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="409984384"/>
-        <c:axId val="457925760"/>
+        <c:axId val="66710144"/>
+        <c:axId val="79589760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="409984384"/>
+        <c:axId val="66710144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6008,14 +6072,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="457925760"/>
+        <c:crossAx val="79589760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="457925760"/>
+        <c:axId val="79589760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6066,7 +6130,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="409984384"/>
+        <c:crossAx val="66710144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9063,7 +9127,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1231"/>
+  <dimension ref="A1:D1249"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -28674,7 +28738,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1231" si="8">A1226+1</f>
+        <f t="shared" ref="A1227:A1249" si="8">A1226+1</f>
         <v>1225</v>
       </c>
       <c r="B1227" s="30" t="s">
@@ -28750,6 +28814,294 @@
       <c r="D1231" s="18">
         <f>SUM(C$3:C1231)/A1231</f>
         <v>26.252550181051159</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4">
+      <c r="A1232" s="18">
+        <f t="shared" si="8"/>
+        <v>1230</v>
+      </c>
+      <c r="B1232" s="30" t="s">
+        <v>975</v>
+      </c>
+      <c r="C1232" s="31">
+        <v>34.16999817</v>
+      </c>
+      <c r="D1232" s="18">
+        <f>SUM(C$3:C1232)/A1232</f>
+        <v>26.258987130635671</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4">
+      <c r="A1233" s="18">
+        <f t="shared" si="8"/>
+        <v>1231</v>
+      </c>
+      <c r="B1233" s="30" t="s">
+        <v>976</v>
+      </c>
+      <c r="C1233" s="31">
+        <v>34.459999080000003</v>
+      </c>
+      <c r="D1233" s="18">
+        <f>SUM(C$3:C1233)/A1233</f>
+        <v>26.265649203705831</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4">
+      <c r="A1234" s="18">
+        <f t="shared" si="8"/>
+        <v>1232</v>
+      </c>
+      <c r="B1234" s="30" t="s">
+        <v>977</v>
+      </c>
+      <c r="C1234" s="31">
+        <v>34.240001679999999</v>
+      </c>
+      <c r="D1234" s="18">
+        <f>SUM(C$3:C1234)/A1234</f>
+        <v>26.272121892404122</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4">
+      <c r="A1235" s="18">
+        <f t="shared" si="8"/>
+        <v>1233</v>
+      </c>
+      <c r="B1235" s="30" t="s">
+        <v>978</v>
+      </c>
+      <c r="C1235" s="31">
+        <v>35.180000309999997</v>
+      </c>
+      <c r="D1235" s="18">
+        <f>SUM(C$3:C1235)/A1235</f>
+        <v>26.27934644910939</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4">
+      <c r="A1236" s="18">
+        <f t="shared" si="8"/>
+        <v>1234</v>
+      </c>
+      <c r="B1236" s="30" t="s">
+        <v>979</v>
+      </c>
+      <c r="C1236" s="31">
+        <v>35.060001370000002</v>
+      </c>
+      <c r="D1236" s="18">
+        <f>SUM(C$3:C1236)/A1236</f>
+        <v>26.286462052772993</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4">
+      <c r="A1237" s="18">
+        <f t="shared" si="8"/>
+        <v>1235</v>
+      </c>
+      <c r="B1237" s="30" t="s">
+        <v>980</v>
+      </c>
+      <c r="C1237" s="31">
+        <v>35.630001069999999</v>
+      </c>
+      <c r="D1237" s="18">
+        <f>SUM(C$3:C1237)/A1237</f>
+        <v>26.294027671410426</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4">
+      <c r="A1238" s="18">
+        <f t="shared" si="8"/>
+        <v>1236</v>
+      </c>
+      <c r="B1238" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="C1238" s="31">
+        <v>35.060001370000002</v>
+      </c>
+      <c r="D1238" s="18">
+        <f>SUM(C$3:C1238)/A1238</f>
+        <v>26.301119883140675</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4">
+      <c r="A1239" s="18">
+        <f t="shared" si="8"/>
+        <v>1237</v>
+      </c>
+      <c r="B1239" s="30" t="s">
+        <v>982</v>
+      </c>
+      <c r="C1239" s="31">
+        <v>34.909999849999998</v>
+      </c>
+      <c r="D1239" s="18">
+        <f>SUM(C$3:C1239)/A1239</f>
+        <v>26.308079365733121</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4">
+      <c r="A1240" s="18">
+        <f t="shared" si="8"/>
+        <v>1238</v>
+      </c>
+      <c r="B1240" s="30" t="s">
+        <v>983</v>
+      </c>
+      <c r="C1240" s="31">
+        <v>34.930000309999997</v>
+      </c>
+      <c r="D1240" s="18">
+        <f>SUM(C$3:C1240)/A1240</f>
+        <v>26.315043760680027</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4">
+      <c r="A1241" s="18">
+        <f t="shared" si="8"/>
+        <v>1239</v>
+      </c>
+      <c r="B1241" s="30" t="s">
+        <v>984</v>
+      </c>
+      <c r="C1241" s="31">
+        <v>35.11000061</v>
+      </c>
+      <c r="D1241" s="18">
+        <f>SUM(C$3:C1241)/A1241</f>
+        <v>26.32214219235825</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4">
+      <c r="A1242" s="18">
+        <f t="shared" si="8"/>
+        <v>1240</v>
+      </c>
+      <c r="B1242" s="30" t="s">
+        <v>985</v>
+      </c>
+      <c r="C1242" s="31">
+        <v>35.11000061</v>
+      </c>
+      <c r="D1242" s="18">
+        <f>SUM(C$3:C1242)/A1242</f>
+        <v>26.32922917495312</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4">
+      <c r="A1243" s="18">
+        <f t="shared" si="8"/>
+        <v>1241</v>
+      </c>
+      <c r="B1243" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="C1243" s="31">
+        <v>35.209999080000003</v>
+      </c>
+      <c r="D1243" s="18">
+        <f>SUM(C$3:C1243)/A1243</f>
+        <v>26.336385315086115</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4">
+      <c r="A1244" s="18">
+        <f t="shared" si="8"/>
+        <v>1242</v>
+      </c>
+      <c r="B1244" s="30" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1244" s="31">
+        <v>35.270000459999999</v>
+      </c>
+      <c r="D1244" s="18">
+        <f>SUM(C$3:C1244)/A1244</f>
+        <v>26.343578241933873</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4">
+      <c r="A1245" s="18">
+        <f t="shared" si="8"/>
+        <v>1243</v>
+      </c>
+      <c r="B1245" s="30" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1245" s="31">
+        <v>35.86000061</v>
+      </c>
+      <c r="D1245" s="18">
+        <f>SUM(C$3:C1245)/A1245</f>
+        <v>26.351234253493057</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4">
+      <c r="A1246" s="18">
+        <f t="shared" si="8"/>
+        <v>1244</v>
+      </c>
+      <c r="B1246" s="30" t="s">
+        <v>989</v>
+      </c>
+      <c r="C1246" s="31">
+        <v>35.77999878</v>
+      </c>
+      <c r="D1246" s="18">
+        <f>SUM(C$3:C1246)/A1246</f>
+        <v>26.358813646199255</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4">
+      <c r="A1247" s="18">
+        <f t="shared" si="8"/>
+        <v>1245</v>
+      </c>
+      <c r="B1247" s="30" t="s">
+        <v>990</v>
+      </c>
+      <c r="C1247" s="31">
+        <v>35.689998629999998</v>
+      </c>
+      <c r="D1247" s="18">
+        <f>SUM(C$3:C1247)/A1247</f>
+        <v>26.366308573897086</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4">
+      <c r="A1248" s="18">
+        <f t="shared" si="8"/>
+        <v>1246</v>
+      </c>
+      <c r="B1248" s="30">
+        <v>46170</v>
+      </c>
+      <c r="C1248" s="31">
+        <v>36.229999540000001</v>
+      </c>
+      <c r="D1248" s="18">
+        <f>SUM(C$3:C1248)/A1248</f>
+        <v>26.374224858781599</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4">
+      <c r="A1249" s="18">
+        <f t="shared" si="8"/>
+        <v>1247</v>
+      </c>
+      <c r="B1249" s="30">
+        <v>46171</v>
+      </c>
+      <c r="C1249" s="31">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D1249" s="18">
+        <f>SUM(C$3:C1249)/A1249</f>
+        <v>26.381551060434539</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -4543,7 +4543,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4768,6 +4768,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4777,7 +4780,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5002,6 +5005,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>152000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5044,7 +5050,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5269,6 +5275,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5278,7 +5287,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5503,6 +5512,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>219124.99999266435</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>237913.37769723308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5545,7 +5557,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5770,6 +5782,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5779,7 +5794,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6004,6 +6019,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>69124.99999266435</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>85913.377697233082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6025,11 +6043,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="66710144"/>
-        <c:axId val="79589760"/>
+        <c:axId val="99719040"/>
+        <c:axId val="103723008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="66710144"/>
+        <c:axId val="99719040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6072,14 +6090,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79589760"/>
+        <c:crossAx val="103723008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79589760"/>
+        <c:axId val="103723008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6130,7 +6148,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66710144"/>
+        <c:crossAx val="99719040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6536,7 +6554,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB77"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9112,6 +9130,35 @@
       </c>
       <c r="I77" s="17">
         <v>69124.99999266435</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="12.75">
+      <c r="A78" s="14">
+        <v>46171</v>
+      </c>
+      <c r="B78" s="15">
+        <v>5.970703125</v>
+      </c>
+      <c r="C78" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D78" s="17">
+        <v>334.9689237814851</v>
+      </c>
+      <c r="E78" s="17">
+        <v>39846.794040230074</v>
+      </c>
+      <c r="F78" s="17">
+        <v>237913.37769723308</v>
+      </c>
+      <c r="G78" s="17">
+        <v>152000</v>
+      </c>
+      <c r="H78" s="17">
+        <v>237913.37769723308</v>
+      </c>
+      <c r="I78" s="17">
+        <v>85913.377697233082</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="1010">
   <si>
     <t>PE</t>
   </si>
@@ -3971,6 +3971,82 @@
   </si>
   <si>
     <t xml:space="preserve">2026/5/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/26
 </t>
   </si>
 </sst>
@@ -6043,11 +6119,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99719040"/>
-        <c:axId val="103723008"/>
+        <c:axId val="305140864"/>
+        <c:axId val="305142784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99719040"/>
+        <c:axId val="305140864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6090,14 +6166,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103723008"/>
+        <c:crossAx val="305142784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103723008"/>
+        <c:axId val="305142784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6148,7 +6224,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99719040"/>
+        <c:crossAx val="305140864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9174,7 +9250,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1249"/>
+  <dimension ref="A1:D1270"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -28785,7 +28861,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1249" si="8">A1226+1</f>
+        <f t="shared" ref="A1227:A1270" si="8">A1226+1</f>
         <v>1225</v>
       </c>
       <c r="B1227" s="30" t="s">
@@ -29149,6 +29225,342 @@
       <c r="D1249" s="18">
         <f>SUM(C$3:C1249)/A1249</f>
         <v>26.381551060434539</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4">
+      <c r="A1250" s="18">
+        <f t="shared" si="8"/>
+        <v>1248</v>
+      </c>
+      <c r="B1250" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="C1250" s="31">
+        <v>34.83000183</v>
+      </c>
+      <c r="D1250" s="18">
+        <f>SUM(C$3:C1250)/A1250</f>
+        <v>26.388320652397333</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4">
+      <c r="A1251" s="18">
+        <f t="shared" si="8"/>
+        <v>1249</v>
+      </c>
+      <c r="B1251" s="30" t="s">
+        <v>992</v>
+      </c>
+      <c r="C1251" s="31">
+        <v>35.590000150000002</v>
+      </c>
+      <c r="D1251" s="18">
+        <f>SUM(C$3:C1251)/A1251</f>
+        <v>26.395687889785322</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4">
+      <c r="A1252" s="18">
+        <f t="shared" si="8"/>
+        <v>1250</v>
+      </c>
+      <c r="B1252" s="30" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1252" s="31">
+        <v>35.950000760000002</v>
+      </c>
+      <c r="D1252" s="18">
+        <f>SUM(C$3:C1252)/A1252</f>
+        <v>26.403331340081493</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4">
+      <c r="A1253" s="18">
+        <f t="shared" si="8"/>
+        <v>1251</v>
+      </c>
+      <c r="B1253" s="30" t="s">
+        <v>994</v>
+      </c>
+      <c r="C1253" s="31">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D1253" s="18">
+        <f>SUM(C$3:C1253)/A1253</f>
+        <v>26.410762730505091</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4">
+      <c r="A1254" s="18">
+        <f t="shared" si="8"/>
+        <v>1252</v>
+      </c>
+      <c r="B1254" s="30" t="s">
+        <v>995</v>
+      </c>
+      <c r="C1254" s="31">
+        <v>34.849998470000003</v>
+      </c>
+      <c r="D1254" s="18">
+        <f>SUM(C$3:C1254)/A1254</f>
+        <v>26.417503334130888</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4">
+      <c r="A1255" s="18">
+        <f t="shared" si="8"/>
+        <v>1253</v>
+      </c>
+      <c r="B1255" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1255" s="31">
+        <v>33.819999690000003</v>
+      </c>
+      <c r="D1255" s="18">
+        <f>SUM(C$3:C1255)/A1255</f>
+        <v>26.423411152451614</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4">
+      <c r="A1256" s="18">
+        <f t="shared" si="8"/>
+        <v>1254</v>
+      </c>
+      <c r="B1256" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1256" s="31">
+        <v>34.659999849999998</v>
+      </c>
+      <c r="D1256" s="18">
+        <f>SUM(C$3:C1256)/A1256</f>
+        <v>26.429979405001493</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4">
+      <c r="A1257" s="18">
+        <f t="shared" si="8"/>
+        <v>1255</v>
+      </c>
+      <c r="B1257" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="C1257" s="31">
+        <v>33.900001529999997</v>
+      </c>
+      <c r="D1257" s="18">
+        <f>SUM(C$3:C1257)/A1257</f>
+        <v>26.435931613866032</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4">
+      <c r="A1258" s="18">
+        <f t="shared" si="8"/>
+        <v>1256</v>
+      </c>
+      <c r="B1258" s="30" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1258" s="31">
+        <v>33.709999080000003</v>
+      </c>
+      <c r="D1258" s="18">
+        <f>SUM(C$3:C1258)/A1258</f>
+        <v>26.441723068854991</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4">
+      <c r="A1259" s="18">
+        <f t="shared" si="8"/>
+        <v>1257</v>
+      </c>
+      <c r="B1259" s="30" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1259" s="31">
+        <v>34.099998470000003</v>
+      </c>
+      <c r="D1259" s="18">
+        <f>SUM(C$3:C1259)/A1259</f>
+        <v>26.447815571162984</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4">
+      <c r="A1260" s="18">
+        <f t="shared" si="8"/>
+        <v>1258</v>
+      </c>
+      <c r="B1260" s="30" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C1260" s="31">
+        <v>39.680000309999997</v>
+      </c>
+      <c r="D1260" s="18">
+        <f>SUM(C$3:C1260)/A1260</f>
+        <v>26.458334001003077</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4">
+      <c r="A1261" s="18">
+        <f t="shared" si="8"/>
+        <v>1259</v>
+      </c>
+      <c r="B1261" s="30" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C1261" s="31">
+        <v>40.299999239999998</v>
+      </c>
+      <c r="D1261" s="18">
+        <f>SUM(C$3:C1261)/A1261</f>
+        <v>26.469328175140486</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4">
+      <c r="A1262" s="18">
+        <f t="shared" si="8"/>
+        <v>1260</v>
+      </c>
+      <c r="B1262" s="30" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1262" s="31">
+        <v>40.819999690000003</v>
+      </c>
+      <c r="D1262" s="18">
+        <f>SUM(C$3:C1262)/A1262</f>
+        <v>26.480717596977676</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4">
+      <c r="A1263" s="18">
+        <f t="shared" si="8"/>
+        <v>1261</v>
+      </c>
+      <c r="B1263" s="30" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C1263" s="31">
+        <v>40.819999690000003</v>
+      </c>
+      <c r="D1263" s="18">
+        <f>SUM(C$3:C1263)/A1263</f>
+        <v>26.492088954704101</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4">
+      <c r="A1264" s="18">
+        <f t="shared" si="8"/>
+        <v>1262</v>
+      </c>
+      <c r="B1264" s="30" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C1264" s="31">
+        <v>42.52999878</v>
+      </c>
+      <c r="D1264" s="18">
+        <f>SUM(C$3:C1264)/A1264</f>
+        <v>26.504797282616384</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4">
+      <c r="A1265" s="18">
+        <f t="shared" si="8"/>
+        <v>1263</v>
+      </c>
+      <c r="B1265" s="30" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C1265" s="31">
+        <v>41.090000150000002</v>
+      </c>
+      <c r="D1265" s="18">
+        <f>SUM(C$3:C1265)/A1265</f>
+        <v>26.516345345060866</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4">
+      <c r="A1266" s="18">
+        <f t="shared" si="8"/>
+        <v>1264</v>
+      </c>
+      <c r="B1266" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C1266" s="31">
+        <v>41.560001370000002</v>
+      </c>
+      <c r="D1266" s="18">
+        <f>SUM(C$3:C1266)/A1266</f>
+        <v>26.528246971662877</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4">
+      <c r="A1267" s="18">
+        <f t="shared" si="8"/>
+        <v>1265</v>
+      </c>
+      <c r="B1267" s="30" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C1267" s="31">
+        <v>42.229999540000001</v>
+      </c>
+      <c r="D1267" s="18">
+        <f>SUM(C$3:C1267)/A1267</f>
+        <v>26.540659424286069</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4">
+      <c r="A1268" s="18">
+        <f t="shared" si="8"/>
+        <v>1266</v>
+      </c>
+      <c r="B1268" s="30" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1268" s="31">
+        <v>40.5</v>
+      </c>
+      <c r="D1268" s="18">
+        <f>SUM(C$3:C1268)/A1268</f>
+        <v>26.551685759653932</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4">
+      <c r="A1269" s="18">
+        <f t="shared" si="8"/>
+        <v>1267</v>
+      </c>
+      <c r="B1269" s="30">
+        <v>46202</v>
+      </c>
+      <c r="C1269" s="31">
+        <v>40.700000760000002</v>
+      </c>
+      <c r="D1269" s="18">
+        <f>SUM(C$3:C1269)/A1269</f>
+        <v>26.562852543395326</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4">
+      <c r="A1270" s="18">
+        <f t="shared" si="8"/>
+        <v>1268</v>
+      </c>
+      <c r="B1270" s="30">
+        <v>46203</v>
+      </c>
+      <c r="C1270" s="31">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D1270" s="18">
+        <f>SUM(C$3:C1270)/A1270</f>
+        <v>26.574869220600849</v>
       </c>
     </row>
   </sheetData>
